--- a/_docs_/trim02/03_estimación_costos/Aleyual_Scrum_Costos.xlsx
+++ b/_docs_/trim02/03_estimación_costos/Aleyual_Scrum_Costos.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">COSTO TOTAL DEL PROYECTO — METODOLOGÍA SCRUM</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2% ahorro</t>
+    <t xml:space="preserve">22.9% ahorro</t>
   </si>
   <si>
     <t xml:space="preserve">  Aleyual — Control Store  |  Costo por Sprint  |  SCRUM — Solo pagas cuando el equipo trabaja</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">Gastos Admin. (4 PCs deprec.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Igual. Servicios + depreciación de 4 PCs trabajadores (PC1/PC2 días, PC4/PC5 18 meses).</t>
+    <t xml:space="preserve">Igual. Servicios + depreciación de 4 PCs trabajadores, ambos por 18 meses trabajados (método uniforme).</t>
   </si>
   <si>
     <t xml:space="preserve">Subtotal base</t>
@@ -644,17 +644,16 @@
     <t xml:space="preserve">AHORRO TOTAL CON SCRUM</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2% más económico — Ahorro: $59.965.586 COP sin reducir funcionalidades</t>
+    <t xml:space="preserve">22.9% más económico — Ahorro: $59.965.585 COP sin reducir funcionalidades</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\)"/>
-    <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\)"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -923,7 +922,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="69">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -984,15 +983,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1000,18 +999,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1020,11 +1007,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1044,15 +1031,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1092,10 +1079,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1210,10 +1193,6 @@
     </xf>
     <xf numFmtId="164" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1583,13 +1562,13 @@
       <c r="C7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="19" t="n">
-        <v>10006334</v>
-      </c>
-      <c r="E7" s="20" t="n">
-        <v>10006334</v>
-      </c>
-      <c r="F7" s="21" t="n">
+      <c r="D7" s="8" t="n">
+        <v>26928000</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>26928000</v>
+      </c>
+      <c r="F7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="11" t="s">
@@ -1597,33 +1576,33 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="24" t="n">
-        <v>128966077</v>
-      </c>
-      <c r="E8" s="25" t="n">
-        <v>172419400</v>
-      </c>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="21" t="n">
+        <v>145887743</v>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>189341066</v>
+      </c>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
       <c r="D9" s="15" t="n">
-        <v>25793215</v>
+        <v>29177549</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>34483880</v>
-      </c>
-      <c r="F9" s="26"/>
+        <v>37868213</v>
+      </c>
+      <c r="F9" s="23"/>
       <c r="G9" s="18" t="s">
         <v>22</v>
       </c>
@@ -1632,35 +1611,35 @@
       <c r="A10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="19" t="n">
-        <v>23213894</v>
-      </c>
-      <c r="E10" s="20" t="n">
-        <v>31035492</v>
-      </c>
-      <c r="F10" s="27"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="8" t="n">
+        <v>26259794</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>34081392</v>
+      </c>
+      <c r="F10" s="24"/>
       <c r="G10" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="30" t="n">
-        <v>177973186</v>
-      </c>
-      <c r="E11" s="31" t="n">
-        <v>237938772</v>
-      </c>
-      <c r="F11" s="32" t="n">
-        <v>-59965586</v>
-      </c>
-      <c r="G11" s="33" t="s">
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="27" t="n">
+        <v>201325086</v>
+      </c>
+      <c r="E11" s="28" t="n">
+        <v>261290671</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>-59965585</v>
+      </c>
+      <c r="G11" s="30" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1753,13 +1732,13 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="33" t="s">
         <v>39</v>
       </c>
       <c r="D5" s="11" t="n">
@@ -1771,24 +1750,24 @@
       <c r="F5" s="8" t="n">
         <v>10866660</v>
       </c>
-      <c r="G5" s="37" t="n">
+      <c r="G5" s="34" t="n">
         <v>10866660</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="35" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="38" t="s">
         <v>44</v>
       </c>
       <c r="D6" s="18" t="n">
@@ -1797,27 +1776,27 @@
       <c r="E6" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="42" t="n">
+      <c r="F6" s="15" t="n">
         <v>7189995</v>
       </c>
-      <c r="G6" s="43" t="n">
+      <c r="G6" s="39" t="n">
         <v>18056655</v>
       </c>
       <c r="H6" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="38" t="s">
+      <c r="I6" s="35" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="33" t="s">
         <v>47</v>
       </c>
       <c r="D7" s="11" t="n">
@@ -1829,24 +1808,24 @@
       <c r="F7" s="8" t="n">
         <v>5949995</v>
       </c>
-      <c r="G7" s="37" t="n">
+      <c r="G7" s="34" t="n">
         <v>24006650</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="44" t="s">
+      <c r="I7" s="40" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="38" t="s">
         <v>51</v>
       </c>
       <c r="D8" s="18" t="n">
@@ -1855,27 +1834,27 @@
       <c r="E8" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="42" t="n">
+      <c r="F8" s="15" t="n">
         <v>4839991</v>
       </c>
-      <c r="G8" s="43" t="n">
+      <c r="G8" s="39" t="n">
         <v>28846641</v>
       </c>
       <c r="H8" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="I8" s="39" t="s">
+      <c r="I8" s="36" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="33" t="s">
         <v>55</v>
       </c>
       <c r="D9" s="11" t="n">
@@ -1887,24 +1866,24 @@
       <c r="F9" s="8" t="n">
         <v>4949996</v>
       </c>
-      <c r="G9" s="37" t="n">
+      <c r="G9" s="34" t="n">
         <v>33796637</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="I9" s="39" t="s">
+      <c r="I9" s="36" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="38" t="s">
         <v>58</v>
       </c>
       <c r="D10" s="18" t="n">
@@ -1913,27 +1892,27 @@
       <c r="E10" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="42" t="n">
+      <c r="F10" s="15" t="n">
         <v>3873330</v>
       </c>
-      <c r="G10" s="43" t="n">
+      <c r="G10" s="39" t="n">
         <v>37669967</v>
       </c>
       <c r="H10" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="I10" s="39" t="s">
+      <c r="I10" s="36" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="33" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="n">
@@ -1945,227 +1924,227 @@
       <c r="F11" s="8" t="n">
         <v>7833338</v>
       </c>
-      <c r="G11" s="37" t="n">
+      <c r="G11" s="34" t="n">
         <v>45503305</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="I11" s="39" t="s">
+      <c r="I11" s="36" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="38" t="s">
         <v>64</v>
       </c>
       <c r="D12" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="E12" s="40" t="n">
+      <c r="E12" s="37" t="n">
         <v>13</v>
       </c>
-      <c r="F12" s="42" t="n">
+      <c r="F12" s="15" t="n">
         <v>9213337</v>
       </c>
-      <c r="G12" s="43" t="n">
+      <c r="G12" s="39" t="n">
         <v>54716642</v>
       </c>
       <c r="H12" s="18" t="n">
         <v>13</v>
       </c>
-      <c r="I12" s="39" t="s">
+      <c r="I12" s="36" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="35" t="s">
+      <c r="B13" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="33" t="s">
         <v>67</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="32" t="n">
         <v>16</v>
       </c>
       <c r="F13" s="8" t="n">
         <v>5466670</v>
       </c>
-      <c r="G13" s="37" t="n">
+      <c r="G13" s="34" t="n">
         <v>60183312</v>
       </c>
       <c r="H13" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="I13" s="39" t="s">
+      <c r="I13" s="36" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="39" t="s">
+      <c r="A14" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="38" t="s">
         <v>70</v>
       </c>
       <c r="D14" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="E14" s="40" t="n">
+      <c r="E14" s="37" t="n">
         <v>23</v>
       </c>
-      <c r="F14" s="42" t="n">
+      <c r="F14" s="15" t="n">
         <v>12213340</v>
       </c>
-      <c r="G14" s="43" t="n">
+      <c r="G14" s="39" t="n">
         <v>72396652</v>
       </c>
       <c r="H14" s="18" t="n">
         <v>52</v>
       </c>
-      <c r="I14" s="39" t="s">
+      <c r="I14" s="36" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="33" t="s">
         <v>73</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="32" t="n">
         <v>34</v>
       </c>
       <c r="F15" s="8" t="n">
         <v>10933340</v>
       </c>
-      <c r="G15" s="37" t="n">
+      <c r="G15" s="34" t="n">
         <v>83329992</v>
       </c>
       <c r="H15" s="11" t="n">
         <v>86</v>
       </c>
-      <c r="I15" s="39" t="s">
+      <c r="I15" s="36" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="38" t="s">
         <v>76</v>
       </c>
       <c r="D16" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="E16" s="40" t="n">
+      <c r="E16" s="37" t="n">
         <v>31</v>
       </c>
-      <c r="F16" s="42" t="n">
+      <c r="F16" s="15" t="n">
         <v>10173338</v>
       </c>
-      <c r="G16" s="43" t="n">
+      <c r="G16" s="39" t="n">
         <v>93503330</v>
       </c>
       <c r="H16" s="18" t="n">
         <v>117</v>
       </c>
-      <c r="I16" s="39" t="s">
+      <c r="I16" s="36" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="33" t="s">
         <v>79</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="32" t="n">
         <v>26</v>
       </c>
       <c r="F17" s="8" t="n">
         <v>9373340</v>
       </c>
-      <c r="G17" s="37" t="n">
+      <c r="G17" s="34" t="n">
         <v>102876670</v>
       </c>
       <c r="H17" s="11" t="n">
         <v>143</v>
       </c>
-      <c r="I17" s="39" t="s">
+      <c r="I17" s="36" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="39" t="s">
+      <c r="A18" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="38" t="s">
         <v>82</v>
       </c>
       <c r="D18" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="E18" s="40" t="n">
+      <c r="E18" s="37" t="n">
         <v>26</v>
       </c>
-      <c r="F18" s="42" t="n">
+      <c r="F18" s="15" t="n">
         <v>6100005</v>
       </c>
-      <c r="G18" s="43" t="n">
+      <c r="G18" s="39" t="n">
         <v>108976675</v>
       </c>
       <c r="H18" s="18" t="n">
         <v>169</v>
       </c>
-      <c r="I18" s="39" t="s">
+      <c r="I18" s="36" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="33" t="s">
         <v>85</v>
       </c>
       <c r="D19" s="11" t="n">
@@ -2177,24 +2156,24 @@
       <c r="F19" s="8" t="n">
         <v>4323336</v>
       </c>
-      <c r="G19" s="37" t="n">
+      <c r="G19" s="34" t="n">
         <v>113300011</v>
       </c>
       <c r="H19" s="11" t="n">
         <v>169</v>
       </c>
-      <c r="I19" s="39" t="s">
+      <c r="I19" s="36" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="38" t="s">
         <v>88</v>
       </c>
       <c r="D20" s="18" t="n">
@@ -2203,37 +2182,37 @@
       <c r="E20" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F20" s="42" t="n">
+      <c r="F20" s="15" t="n">
         <v>4979999</v>
       </c>
-      <c r="G20" s="43" t="n">
+      <c r="G20" s="39" t="n">
         <v>118280010</v>
       </c>
       <c r="H20" s="18" t="n">
         <v>169</v>
       </c>
-      <c r="I20" s="39" t="s">
+      <c r="I20" s="36" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="45" t="n">
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="41" t="n">
         <v>118280010</v>
       </c>
-      <c r="G21" s="46" t="n">
+      <c r="G21" s="42" t="n">
         <v>118280010</v>
       </c>
-      <c r="H21" s="47" t="n">
+      <c r="H21" s="43" t="n">
         <v>169</v>
       </c>
-      <c r="I21" s="33" t="s">
+      <c r="I21" s="30" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2311,526 +2290,526 @@
     </row>
     <row r="3" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="49" t="s">
+      <c r="C4" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="49" t="s">
+      <c r="D4" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="49" t="s">
+      <c r="E4" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="49" t="s">
+      <c r="F4" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="49" t="s">
+      <c r="G4" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="49" t="s">
+      <c r="H4" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="49" t="s">
+      <c r="I4" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="J4" s="49" t="s">
+      <c r="J4" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="K4" s="49" t="s">
+      <c r="K4" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="L4" s="49" t="s">
+      <c r="L4" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="49" t="s">
+      <c r="M4" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="N4" s="49" t="s">
+      <c r="N4" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="O4" s="49" t="s">
+      <c r="O4" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="P4" s="49" t="s">
+      <c r="P4" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="Q4" s="49" t="s">
+      <c r="Q4" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="R4" s="49" t="s">
+      <c r="R4" s="45" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="D5" s="51" t="s">
+      <c r="D5" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="51" t="s">
+      <c r="G5" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="K5" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="51" t="s">
+      <c r="K5" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="M5" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="O5" s="51" t="s">
+      <c r="M5" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="P5" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q5" s="51" t="s">
+      <c r="P5" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q5" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="R5" s="51" t="s">
+      <c r="R5" s="47" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="D6" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="F6" s="51" t="s">
+      <c r="F6" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="G6" s="51" t="s">
+      <c r="G6" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="I6" s="51" t="s">
+      <c r="I6" s="47" t="s">
         <v>108</v>
       </c>
-      <c r="J6" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="K6" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="N6" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="O6" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="P6" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q6" s="51" t="s">
+      <c r="J6" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="K6" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="L6" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="O6" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="P6" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q6" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="R6" s="51" t="s">
+      <c r="R6" s="47" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="46" t="s">
         <v>111</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="F7" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="N7" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="O7" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="P7" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q7" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="R7" s="52" t="s">
+      <c r="F7" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="N7" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="O7" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="P7" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q7" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="R7" s="48" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="B8" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="C8" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="51" t="s">
+      <c r="C8" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="G8" s="51" t="s">
+      <c r="G8" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="51" t="s">
+      <c r="H8" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="I8" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" s="51" t="s">
+      <c r="I8" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="K8" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="L8" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="M8" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="N8" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="O8" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="P8" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q8" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="R8" s="54" t="s">
+      <c r="K8" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="N8" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="O8" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="P8" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q8" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="R8" s="50" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="51" t="s">
+      <c r="C9" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="H9" s="51" t="s">
+      <c r="H9" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="I9" s="51" t="s">
+      <c r="I9" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="J9" s="51" t="s">
+      <c r="J9" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="K9" s="51" t="s">
+      <c r="K9" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="L9" s="51" t="s">
+      <c r="L9" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="M9" s="51" t="s">
+      <c r="M9" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="N9" s="51" t="s">
+      <c r="N9" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="O9" s="51" t="s">
+      <c r="O9" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="P9" s="51" t="s">
+      <c r="P9" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="Q9" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="R9" s="52" t="s">
+      <c r="Q9" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="R9" s="48" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="C10" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" s="51" t="s">
+      <c r="C10" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="J10" s="51" t="s">
+      <c r="J10" s="47" t="s">
         <v>127</v>
       </c>
-      <c r="K10" s="51" t="s">
+      <c r="K10" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="L10" s="51" t="s">
+      <c r="L10" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="M10" s="51" t="s">
+      <c r="M10" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="N10" s="51" t="s">
+      <c r="N10" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="O10" s="51" t="s">
+      <c r="O10" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="P10" s="51" t="s">
+      <c r="P10" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="Q10" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="R10" s="54" t="s">
+      <c r="Q10" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="R10" s="50" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="C11" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="K11" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="L11" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="M11" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="N11" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="O11" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="P11" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q11" s="51" t="s">
+      <c r="C11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="K11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="L11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="N11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="O11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q11" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="R11" s="51" t="s">
+      <c r="R11" s="47" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="55"/>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="55"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="55"/>
-      <c r="N12" s="55"/>
-      <c r="O12" s="55"/>
-      <c r="P12" s="55"/>
-      <c r="Q12" s="55"/>
-      <c r="R12" s="55"/>
+      <c r="A12" s="51"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="51"/>
+      <c r="O12" s="51"/>
+      <c r="P12" s="51"/>
+      <c r="Q12" s="51"/>
+      <c r="R12" s="51"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="53" t="s">
         <v>136</v>
       </c>
-      <c r="C13" s="58" t="n">
+      <c r="C13" s="54" t="n">
         <v>10866660</v>
       </c>
-      <c r="D13" s="58" t="n">
+      <c r="D13" s="54" t="n">
         <v>7189995</v>
       </c>
-      <c r="E13" s="58" t="n">
+      <c r="E13" s="54" t="n">
         <v>5949995</v>
       </c>
-      <c r="F13" s="58" t="n">
+      <c r="F13" s="54" t="n">
         <v>4839991</v>
       </c>
-      <c r="G13" s="58" t="n">
+      <c r="G13" s="54" t="n">
         <v>4949996</v>
       </c>
-      <c r="H13" s="58" t="n">
+      <c r="H13" s="54" t="n">
         <v>3873330</v>
       </c>
-      <c r="I13" s="58" t="n">
+      <c r="I13" s="54" t="n">
         <v>7833338</v>
       </c>
-      <c r="J13" s="58" t="n">
+      <c r="J13" s="54" t="n">
         <v>9213337</v>
       </c>
-      <c r="K13" s="58" t="n">
+      <c r="K13" s="54" t="n">
         <v>5466670</v>
       </c>
-      <c r="L13" s="58" t="n">
+      <c r="L13" s="54" t="n">
         <v>12213340</v>
       </c>
-      <c r="M13" s="58" t="n">
+      <c r="M13" s="54" t="n">
         <v>10933340</v>
       </c>
-      <c r="N13" s="58" t="n">
+      <c r="N13" s="54" t="n">
         <v>10173338</v>
       </c>
-      <c r="O13" s="58" t="n">
+      <c r="O13" s="54" t="n">
         <v>9373340</v>
       </c>
-      <c r="P13" s="58" t="n">
+      <c r="P13" s="54" t="n">
         <v>6100005</v>
       </c>
-      <c r="Q13" s="58" t="n">
+      <c r="Q13" s="54" t="n">
         <v>4323336</v>
       </c>
-      <c r="R13" s="58" t="n">
+      <c r="R13" s="54" t="n">
         <v>4979999</v>
       </c>
     </row>
@@ -2901,16 +2880,16 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="31" t="s">
         <v>42</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="D4" s="56" t="s">
         <v>40</v>
       </c>
       <c r="E4" s="8" t="n">
@@ -2924,19 +2903,19 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="36" t="s">
         <v>45</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="62" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="42" t="n">
+      <c r="D5" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="15" t="n">
         <v>7189995</v>
       </c>
       <c r="F5" s="18" t="s">
@@ -2947,16 +2926,16 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="31" t="s">
         <v>49</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="56" t="s">
         <v>40</v>
       </c>
       <c r="E6" s="8" t="n">
@@ -2970,19 +2949,19 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="36" t="s">
         <v>53</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="61" t="s">
+      <c r="C7" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="62" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="42" t="n">
+      <c r="D7" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="15" t="n">
         <v>4839991</v>
       </c>
       <c r="F7" s="18" t="s">
@@ -2993,16 +2972,16 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="31" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="C8" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="60" t="s">
+      <c r="D8" s="56" t="s">
         <v>40</v>
       </c>
       <c r="E8" s="8" t="n">
@@ -3016,19 +2995,19 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="36" t="s">
         <v>59</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C9" s="61" t="s">
+      <c r="C9" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="62" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="42" t="n">
+      <c r="D9" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="15" t="n">
         <v>3873330</v>
       </c>
       <c r="F9" s="18" t="s">
@@ -3039,16 +3018,16 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="31" t="s">
         <v>62</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="60" t="s">
+      <c r="D10" s="56" t="s">
         <v>40</v>
       </c>
       <c r="E10" s="8" t="n">
@@ -3062,39 +3041,39 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="36" t="s">
         <v>65</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="63" t="n">
+      <c r="D11" s="59" t="n">
         <v>13</v>
       </c>
-      <c r="E11" s="42" t="n">
+      <c r="E11" s="15" t="n">
         <v>9213337</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="G11" s="64" t="n">
+      <c r="G11" s="60" t="n">
         <v>708718</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="31" t="s">
         <v>68</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="C12" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="65" t="n">
+      <c r="D12" s="61" t="n">
         <v>16</v>
       </c>
       <c r="E12" s="8" t="n">
@@ -3103,44 +3082,44 @@
       <c r="F12" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="G12" s="66" t="n">
+      <c r="G12" s="62" t="n">
         <v>341667</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="36" t="s">
         <v>71</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="63" t="n">
+      <c r="D13" s="59" t="n">
         <v>23</v>
       </c>
-      <c r="E13" s="42" t="n">
+      <c r="E13" s="15" t="n">
         <v>12213340</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="G13" s="64" t="n">
+      <c r="G13" s="60" t="n">
         <v>531015</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="31" t="s">
         <v>74</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="65" t="n">
+      <c r="D14" s="61" t="n">
         <v>34</v>
       </c>
       <c r="E14" s="8" t="n">
@@ -3149,44 +3128,44 @@
       <c r="F14" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="G14" s="66" t="n">
+      <c r="G14" s="62" t="n">
         <v>321569</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="36" t="s">
         <v>77</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="C15" s="61" t="s">
+      <c r="C15" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="63" t="n">
+      <c r="D15" s="59" t="n">
         <v>31</v>
       </c>
-      <c r="E15" s="42" t="n">
+      <c r="E15" s="15" t="n">
         <v>10173338</v>
       </c>
       <c r="F15" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="G15" s="64" t="n">
+      <c r="G15" s="60" t="n">
         <v>328172</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="31" t="s">
         <v>80</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="55" t="s">
         <v>167</v>
       </c>
-      <c r="D16" s="65" t="n">
+      <c r="D16" s="61" t="n">
         <v>52</v>
       </c>
       <c r="E16" s="8" t="n">
@@ -3195,24 +3174,24 @@
       <c r="F16" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="G16" s="66" t="n">
+      <c r="G16" s="62" t="n">
         <v>297564</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="36" t="s">
         <v>83</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="62" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="42" t="n">
+      <c r="D17" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="15" t="n">
         <v>4323336</v>
       </c>
       <c r="F17" s="18" t="s">
@@ -3223,16 +3202,16 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="31" t="s">
         <v>86</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C18" s="59" t="s">
+      <c r="C18" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="60" t="s">
+      <c r="D18" s="56" t="s">
         <v>40</v>
       </c>
       <c r="E18" s="8" t="n">
@@ -3246,21 +3225,21 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="47" t="n">
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="43" t="n">
         <v>175</v>
       </c>
-      <c r="E19" s="45" t="n">
+      <c r="E19" s="41" t="n">
         <v>118280010</v>
       </c>
-      <c r="F19" s="33" t="s">
+      <c r="F19" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="G19" s="46" t="n">
+      <c r="G19" s="42" t="n">
         <v>675886</v>
       </c>
     </row>
@@ -3323,10 +3302,10 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="63" t="s">
         <v>179</v>
       </c>
       <c r="C4" s="10" t="n">
@@ -3338,15 +3317,15 @@
       <c r="E4" s="10" t="n">
         <v>-43453323</v>
       </c>
-      <c r="F4" s="68" t="s">
+      <c r="F4" s="64" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="65" t="s">
         <v>181</v>
       </c>
       <c r="C5" s="17" t="n">
@@ -3358,185 +3337,185 @@
       <c r="E5" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="70" t="s">
+      <c r="F5" s="66" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="63" t="s">
         <v>183</v>
       </c>
-      <c r="C6" s="21" t="n">
-        <v>10006334</v>
-      </c>
-      <c r="D6" s="20" t="n">
-        <v>10006334</v>
-      </c>
-      <c r="E6" s="21" t="n">
+      <c r="C6" s="10" t="n">
+        <v>26928000</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>26928000</v>
+      </c>
+      <c r="E6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="68" t="s">
+      <c r="F6" s="64" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="65" t="s">
         <v>185</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>128966077</v>
+        <v>145887743</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>172419400</v>
+        <v>189341066</v>
       </c>
       <c r="E7" s="17" t="n">
         <v>-43453323</v>
       </c>
-      <c r="F7" s="70" t="s">
+      <c r="F7" s="66" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="34" t="s">
+      <c r="A8" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="67" t="s">
+      <c r="B8" s="63" t="s">
         <v>187</v>
       </c>
-      <c r="C8" s="21" t="n">
-        <v>25793215</v>
-      </c>
-      <c r="D8" s="20" t="n">
-        <v>34483880</v>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>-8690665</v>
-      </c>
-      <c r="F8" s="68" t="s">
+      <c r="C8" s="10" t="n">
+        <v>29177549</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>37868213</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>-8690664</v>
+      </c>
+      <c r="F8" s="64" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="39" t="s">
+      <c r="A9" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="65" t="s">
         <v>189</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>23213894</v>
+        <v>26259794</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>31035492</v>
+        <v>34081392</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>-7821598</v>
       </c>
-      <c r="F9" s="70" t="s">
+      <c r="F9" s="66" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="31" t="s">
         <v>62</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="C10" s="19" t="n">
-        <v>177973186</v>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>237938772</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-59965586</v>
-      </c>
-      <c r="F10" s="68" t="s">
+      <c r="C10" s="8" t="n">
+        <v>201325086</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>261290671</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>-59965585</v>
+      </c>
+      <c r="F10" s="64" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="65" t="s">
         <v>193</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="F11" s="70" t="s">
+      <c r="F11" s="66" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="63" t="s">
         <v>197</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="F12" s="68" t="s">
+      <c r="F12" s="64" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="65" t="s">
         <v>201</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="36" t="s">
         <v>203</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="F13" s="70" t="s">
+      <c r="F13" s="66" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="71" t="s">
+      <c r="A14" s="67" t="s">
         <v>205</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="32" t="n">
-        <v>177973186</v>
-      </c>
-      <c r="D14" s="31" t="n">
-        <v>237938772</v>
-      </c>
-      <c r="E14" s="72" t="n">
-        <v>-59965586</v>
-      </c>
-      <c r="F14" s="73" t="s">
+      <c r="B14" s="26"/>
+      <c r="C14" s="29" t="n">
+        <v>201325086</v>
+      </c>
+      <c r="D14" s="28" t="n">
+        <v>261290671</v>
+      </c>
+      <c r="E14" s="41" t="n">
+        <v>-59965585</v>
+      </c>
+      <c r="F14" s="68" t="s">
         <v>206</v>
       </c>
     </row>

--- a/_docs_/trim02/03_estimación_costos/Aleyual_Scrum_Costos.xlsx
+++ b/_docs_/trim02/03_estimación_costos/Aleyual_Scrum_Costos.xlsx
@@ -209,7 +209,7 @@
     <t xml:space="preserve">S6</t>
   </si>
   <si>
-    <t xml:space="preserve">Frontend base React + configuración JWT</t>
+    <t xml:space="preserve">Frontend base Blade + configuración Sanctum</t>
   </si>
   <si>
     <t xml:space="preserve">7</t>
